--- a/prisma/sample/sample_huli.xlsx
+++ b/prisma/sample/sample_huli.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Citas" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Sheet2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
   <si>
     <t>Fecha</t>
   </si>
@@ -61,25 +61,25 @@
     <t>ID cita</t>
   </si>
   <si>
-    <t>2026-10-05</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Paciente Importado Uno</t>
-  </si>
-  <si>
-    <t>5500000001</t>
-  </si>
-  <si>
-    <t>Particular</t>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>9:00 AM</t>
+  </si>
+  <si>
+    <t>9:30 AM</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>Paciente Mañana Uno</t>
+  </si>
+  <si>
+    <t>(+52) 5510000001</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>1990-01-15</t>
@@ -94,10 +94,7 @@
     <t>Confirmada</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Revisión</t>
+    <t>1°</t>
   </si>
   <si>
     <t>DermaMx</t>
@@ -106,61 +103,112 @@
     <t>Berenice Gomez Tagle Boix</t>
   </si>
   <si>
-    <t>HULI-IMP-001</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>Paciente Importado Dos</t>
-  </si>
-  <si>
-    <t>5500000002</t>
-  </si>
-  <si>
-    <t>Seguro XYZ</t>
+    <t>80159501</t>
+  </si>
+  <si>
+    <t>1:00 PM</t>
+  </si>
+  <si>
+    <t>1:30 PM</t>
+  </si>
+  <si>
+    <t>Paciente Tarde Dos</t>
+  </si>
+  <si>
+    <t>(+52) 5510000002</t>
   </si>
   <si>
     <t>1985-05-20</t>
   </si>
   <si>
-    <t>import2@test.com</t>
+    <t>Completada</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>Luisa Fernanda Martínez Rosas Hijar</t>
+  </si>
+  <si>
+    <t>80159502</t>
+  </si>
+  <si>
+    <t>4:00 PM</t>
+  </si>
+  <si>
+    <t>4:30 PM</t>
+  </si>
+  <si>
+    <t>(+52) 5510000003</t>
   </si>
   <si>
     <t>Sin confirmar</t>
   </si>
   <si>
-    <t>Láser</t>
-  </si>
-  <si>
-    <t>Carlos Mendoza Ruiz</t>
-  </si>
-  <si>
-    <t>HULI-IMP-002</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>16:30</t>
+    <t>María Alejandra Chacón Ruiz</t>
+  </si>
+  <si>
+    <t>80159503</t>
+  </si>
+  <si>
+    <t>6:30 PM</t>
+  </si>
+  <si>
+    <t>7:00 PM</t>
   </si>
   <si>
     <t>Paciente Cancelado</t>
   </si>
   <si>
-    <t>5500000003</t>
+    <t>(+52) 5510000004</t>
   </si>
   <si>
     <t>Cancelada</t>
   </si>
   <si>
-    <t>Ana Patricia Solís</t>
-  </si>
-  <si>
-    <t>HULI-IMP-003</t>
+    <t>80159504</t>
+  </si>
+  <si>
+    <t>2:00 PM</t>
+  </si>
+  <si>
+    <t>2:30 PM</t>
+  </si>
+  <si>
+    <t>Paciente No Show</t>
+  </si>
+  <si>
+    <t>(+52) 5510000005</t>
+  </si>
+  <si>
+    <t>Paciente no se presentó</t>
+  </si>
+  <si>
+    <t>80159505</t>
+  </si>
+  <si>
+    <t>3:00 PM</t>
+  </si>
+  <si>
+    <t>3:30 PM</t>
+  </si>
+  <si>
+    <t>Paciente Reagendado</t>
+  </si>
+  <si>
+    <t>(+52) 5510000006</t>
+  </si>
+  <si>
+    <t>ferickg.sk@example.com</t>
+  </si>
+  <si>
+    <t>Reagendada</t>
+  </si>
+  <si>
+    <t>1° Retiro de verrugas</t>
+  </si>
+  <si>
+    <t>80159506</t>
   </si>
 </sst>
 </file>
@@ -537,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -625,19 +673,19 @@
         <v>26</v>
       </c>
       <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>30</v>
-      </c>
-      <c r="P2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -645,49 +693,49 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
         <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
         <v>35</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
         <v>38</v>
       </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="P3" t="s">
         <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -695,49 +743,199 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M4" t="s">
         <v>27</v>
       </c>
       <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" t="s">
         <v>29</v>
       </c>
-      <c r="O4" t="s">
-        <v>48</v>
-      </c>
-      <c r="P4" t="s">
-        <v>49</v>
+      <c r="P5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
